--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/NEBRASKA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/NEBRASKA_2022.xlsx
@@ -553,7 +553,7 @@
         <v>3</v>
       </c>
       <c r="D11">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="12">
@@ -1003,7 +1003,7 @@
         <v>3</v>
       </c>
       <c r="D36">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="37">
@@ -1021,7 +1021,7 @@
         <v>3</v>
       </c>
       <c r="D37">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="38">
@@ -1345,7 +1345,7 @@
         <v>3</v>
       </c>
       <c r="D55">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="56">
@@ -1471,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="D62">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="63">
@@ -1543,7 +1543,7 @@
         <v>3</v>
       </c>
       <c r="D66">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="67">
@@ -1705,7 +1705,7 @@
         <v>3</v>
       </c>
       <c r="D75">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="76">
@@ -1741,7 +1741,7 @@
         <v>3</v>
       </c>
       <c r="D77">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="78">
@@ -2083,7 +2083,7 @@
         <v>3</v>
       </c>
       <c r="D96">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="97">
@@ -2256,14 +2256,14 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C106">
         <v>3</v>
       </c>
       <c r="D106">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="107">
@@ -2479,7 +2479,7 @@
         <v>3</v>
       </c>
       <c r="D118">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="119">
@@ -2713,7 +2713,7 @@
         <v>3</v>
       </c>
       <c r="D131">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="132">
@@ -3019,7 +3019,7 @@
         <v>3</v>
       </c>
       <c r="D148">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="149">
@@ -3073,7 +3073,7 @@
         <v>3</v>
       </c>
       <c r="D151">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="152">
@@ -3307,7 +3307,7 @@
         <v>3</v>
       </c>
       <c r="D164">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="165">
@@ -3415,7 +3415,7 @@
         <v>3</v>
       </c>
       <c r="D170">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="171">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C175">
@@ -3613,7 +3613,7 @@
         <v>3</v>
       </c>
       <c r="D181">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="182">
@@ -3624,14 +3624,14 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C182">
         <v>3</v>
       </c>
       <c r="D182">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="183">
@@ -3919,7 +3919,7 @@
         <v>3</v>
       </c>
       <c r="D198">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="199">
@@ -4513,7 +4513,7 @@
         <v>3</v>
       </c>
       <c r="D231">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="232">
@@ -4531,7 +4531,7 @@
         <v>3</v>
       </c>
       <c r="D232">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="233">
@@ -4603,7 +4603,7 @@
         <v>3</v>
       </c>
       <c r="D236">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="237">
@@ -4675,7 +4675,7 @@
         <v>3</v>
       </c>
       <c r="D240">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="241">
@@ -4711,7 +4711,7 @@
         <v>3</v>
       </c>
       <c r="D242">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="243">
@@ -4729,7 +4729,7 @@
         <v>3</v>
       </c>
       <c r="D243">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="244">
@@ -4783,7 +4783,7 @@
         <v>3</v>
       </c>
       <c r="D246">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="247">
@@ -5125,7 +5125,7 @@
         <v>3</v>
       </c>
       <c r="D265">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="266">
@@ -5179,7 +5179,7 @@
         <v>3</v>
       </c>
       <c r="D268">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="269">
@@ -5413,7 +5413,7 @@
         <v>3</v>
       </c>
       <c r="D281">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="282">
@@ -5611,7 +5611,7 @@
         <v>3</v>
       </c>
       <c r="D292">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="293">
@@ -5773,7 +5773,7 @@
         <v>3</v>
       </c>
       <c r="D301">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="302">
@@ -6079,7 +6079,7 @@
         <v>3</v>
       </c>
       <c r="D318">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="319">
@@ -6205,7 +6205,7 @@
         <v>3</v>
       </c>
       <c r="D325">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="326">
@@ -6223,7 +6223,7 @@
         <v>3</v>
       </c>
       <c r="D326">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="327">
@@ -6259,7 +6259,7 @@
         <v>3</v>
       </c>
       <c r="D328">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="329">
@@ -6313,7 +6313,7 @@
         <v>3</v>
       </c>
       <c r="D331">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="332">
@@ -6349,7 +6349,7 @@
         <v>3</v>
       </c>
       <c r="D333">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="334">
@@ -6385,7 +6385,7 @@
         <v>3</v>
       </c>
       <c r="D335">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="336">
@@ -6457,7 +6457,7 @@
         <v>3</v>
       </c>
       <c r="D339">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="340">
@@ -6511,7 +6511,7 @@
         <v>3</v>
       </c>
       <c r="D342">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="343">
@@ -6709,7 +6709,7 @@
         <v>3</v>
       </c>
       <c r="D353">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="354">
@@ -6763,7 +6763,7 @@
         <v>3</v>
       </c>
       <c r="D356">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="357">
@@ -6997,7 +6997,7 @@
         <v>3</v>
       </c>
       <c r="D369">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="370">
@@ -7159,7 +7159,7 @@
         <v>3</v>
       </c>
       <c r="D378">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="379">
@@ -7285,7 +7285,7 @@
         <v>3</v>
       </c>
       <c r="D385">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="386">
@@ -8023,7 +8023,7 @@
         <v>3</v>
       </c>
       <c r="D426">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="427">
@@ -8419,7 +8419,7 @@
         <v>3</v>
       </c>
       <c r="D448">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="449">
@@ -8563,7 +8563,7 @@
         <v>3</v>
       </c>
       <c r="D456">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="457">
@@ -8797,7 +8797,7 @@
         <v>3</v>
       </c>
       <c r="D469">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="470">
@@ -9031,7 +9031,7 @@
         <v>3</v>
       </c>
       <c r="D482">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="483">
@@ -9085,7 +9085,7 @@
         <v>3</v>
       </c>
       <c r="D485">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="486">
@@ -9571,7 +9571,7 @@
         <v>3</v>
       </c>
       <c r="D512">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="513">
@@ -10489,7 +10489,7 @@
         <v>3</v>
       </c>
       <c r="D563">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="564">
@@ -10723,7 +10723,7 @@
         <v>3</v>
       </c>
       <c r="D576">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="577">
@@ -10741,7 +10741,7 @@
         <v>3</v>
       </c>
       <c r="D577">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="578">
@@ -10867,7 +10867,7 @@
         <v>3</v>
       </c>
       <c r="D584">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="585">
@@ -10885,7 +10885,7 @@
         <v>3</v>
       </c>
       <c r="D585">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="586">
@@ -10921,7 +10921,7 @@
         <v>3</v>
       </c>
       <c r="D587">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="588">
@@ -10975,7 +10975,7 @@
         <v>3</v>
       </c>
       <c r="D590">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="591">
@@ -11083,7 +11083,7 @@
         <v>3</v>
       </c>
       <c r="D596">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="597">
@@ -11155,7 +11155,7 @@
         <v>3</v>
       </c>
       <c r="D600">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="601">
@@ -11533,7 +11533,7 @@
         <v>3</v>
       </c>
       <c r="D621">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="622">
@@ -12091,7 +12091,7 @@
         <v>3</v>
       </c>
       <c r="D652">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="653">
@@ -12343,7 +12343,7 @@
         <v>3</v>
       </c>
       <c r="D666">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="667">
@@ -12379,7 +12379,7 @@
         <v>3</v>
       </c>
       <c r="D668">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="669">
@@ -12415,7 +12415,7 @@
         <v>3</v>
       </c>
       <c r="D670">
-        <v>0.0009389671361502347</v>
+        <v>0.0009389671361502348</v>
       </c>
     </row>
     <row r="671">
